--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487055_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487055_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1411</v>
+        <v>1.3602</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1125</v>
+        <v>0.3316</v>
       </c>
       <c r="F2" t="n">
         <v>1.0286</v>
@@ -610,10 +610,10 @@
         <v>0.772</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3715</v>
+        <v>-0.1524</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5949</v>
+        <v>-0.3758</v>
       </c>
       <c r="U2" t="n">
         <v>0.2234</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9029</v>
+        <v>0.6272</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3028</v>
+        <v>2.0807</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3999</v>
+        <v>-1.4535</v>
       </c>
       <c r="G3" t="n">
         <v>1.428</v>
@@ -688,13 +688,13 @@
         <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>0.201</v>
+        <v>-0.0747</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1507</v>
+        <v>-0.3728</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3516</v>
+        <v>0.2981</v>
       </c>
       <c r="V3" t="n">
         <v>-1.8842</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0233</v>
+        <v>0.5815</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2315</v>
+        <v>0.1661</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2548</v>
+        <v>0.4154</v>
       </c>
       <c r="G4" t="n">
         <v>1.3124</v>
@@ -766,13 +766,13 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5123</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6266</v>
+        <v>-0.229</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8857</v>
+        <v>-0.7251</v>
       </c>
       <c r="V4" t="n">
         <v>-1.5138</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>A. GUTIEZ SALGADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9291</v>
+        <v>-0.4336</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8038</v>
+        <v>-1.7497</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7329</v>
+        <v>1.3161</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.922</v>
+        <v>-1.4465</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5154</v>
+        <v>0.2143</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4066</v>
+        <v>-1.6608</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2602</v>
+        <v>-1.9007</v>
       </c>
       <c r="K5" t="n">
-        <v>0.326</v>
+        <v>0.0207</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-1.9214</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6618</v>
+        <v>0.4542</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8414</v>
+        <v>0.1936</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8204</v>
+        <v>0.2606</v>
       </c>
       <c r="P5" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5281</v>
+        <v>-0.0449</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1639</v>
+        <v>-0.1348</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3642</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9421</v>
+        <v>0.2859</v>
       </c>
       <c r="W5" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GUTIEZ SALGADO</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9412</v>
+        <v>-0.7496</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1502</v>
+        <v>1.0636</v>
       </c>
       <c r="F6" t="n">
-        <v>1.209</v>
+        <v>-1.8132</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4465</v>
+        <v>-1.922</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2143</v>
+        <v>-0.5154</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6608</v>
+        <v>-1.4066</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9007</v>
+        <v>-0.2602</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0207</v>
+        <v>0.326</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9214</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4542</v>
+        <v>-1.6618</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1936</v>
+        <v>-0.8414</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2606</v>
+        <v>-0.8204</v>
       </c>
       <c r="P6" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5526</v>
+        <v>-0.3487</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5354</v>
+        <v>0.0959</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0172</v>
+        <v>-0.4445</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2859</v>
+        <v>0.9421</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5606</v>
+        <v>-1.4744</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.891</v>
+        <v>-0.8315</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6696</v>
+        <v>-0.6428</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6875</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0919</v>
+        <v>0.1781</v>
       </c>
       <c r="T7" t="n">
-        <v>0.074</v>
+        <v>0.1335</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7723</v>
+        <v>-2.0683</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6481</v>
+        <v>-1.1315</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1242</v>
+        <v>-0.9368</v>
       </c>
       <c r="G8" t="n">
         <v>-1.16</v>
@@ -1078,13 +1078,13 @@
         <v>0.772</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.1666</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4614</v>
+        <v>0.0552</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4092</v>
+        <v>-0.2218</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5138</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8796</v>
+        <v>-3.12</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2661</v>
+        <v>-2.1107</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6135</v>
+        <v>-1.0094</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6279</v>
+        <v>-0.6506</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0399</v>
+        <v>-1.6973</v>
       </c>
       <c r="I9" t="n">
-        <v>0.412</v>
+        <v>1.0468</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6812</v>
+        <v>1.2848</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5641</v>
+        <v>0.0723</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2453</v>
+        <v>1.2124</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3091</v>
+        <v>-1.9353</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4758</v>
+        <v>-1.7697</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8333</v>
+        <v>-0.1657</v>
       </c>
       <c r="P9" t="n">
         <v>-0.965</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R9" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4693</v>
+        <v>-0.973</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0172</v>
+        <v>-0.5003</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4521</v>
+        <v>-0.4726</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8173</v>
+        <v>-0.5315</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8173</v>
+        <v>-0.5315</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>P. ALBISU ASTIGARRAGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9529</v>
+        <v>-3.5672</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.89</v>
+        <v>-3.8163</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0629</v>
+        <v>0.2491</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6506</v>
+        <v>-1.6662</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6973</v>
+        <v>-1.6612</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0468</v>
+        <v>-0.005</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2848</v>
+        <v>-1.5396</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0723</v>
+        <v>-1.5474</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2124</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9353</v>
+        <v>-0.1266</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7697</v>
+        <v>-0.1137</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1657</v>
+        <v>-0.0129</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.965</v>
+        <v>-0.386</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8058</v>
+        <v>-0.9835</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2796</v>
+        <v>-0.3467</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5262</v>
+        <v>-0.6369</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5315</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ALBISU ASTIGARRAGA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1046</v>
+        <v>-4.3158</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2734</v>
+        <v>-1.4882</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1688</v>
+        <v>-2.8276</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6662</v>
+        <v>-1.6279</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6612</v>
+        <v>-2.0399</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.005</v>
+        <v>0.412</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5396</v>
+        <v>0.6812</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5474</v>
+        <v>-0.5641</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.2453</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1266</v>
+        <v>-2.3091</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1137</v>
+        <v>-1.4758</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0129</v>
+        <v>-0.8333</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5209</v>
+        <v>-0.9056</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8037</v>
+        <v>-0.2393</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.6663</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5315</v>
+        <v>-0.8173</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5315</v>
+        <v>-0.8173</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8497</v>
+        <v>-4.5215</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.068</v>
+        <v>-3.3918</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7817</v>
+        <v>-1.1297</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3911</v>
@@ -1390,13 +1390,13 @@
         <v>2.3161</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2407</v>
+        <v>-0.9125</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5176</v>
+        <v>-0.8414</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2769</v>
+        <v>-0.0711</v>
       </c>
       <c r="V12" t="n">
         <v>0.3261</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.116400000000001</v>
+        <v>-8.6806</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0364</v>
+        <v>-5.6809</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.08</v>
+        <v>-2.9997</v>
       </c>
       <c r="G13" t="n">
         <v>-4.1796</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1857</v>
+        <v>-0.7499</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7827</v>
+        <v>0.1382</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9684</v>
+        <v>-0.8881</v>
       </c>
       <c r="V13" t="n">
         <v>-2.786</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-29.0391</v>
+        <v>-26.3621</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.2356</v>
+        <v>-16.5586</v>
       </c>
       <c r="F14" t="n">
         <v>-9.8035</v>
@@ -1531,7 +1531,7 @@
         <v>-10.9102</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.014799999999999</v>
+        <v>-8.014800000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-2.8956</v>
@@ -1546,13 +1546,13 @@
         <v>14.4755</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.7645</v>
+        <v>-6.0878</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.2943</v>
+        <v>-2.6173</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.4705</v>
+        <v>-3.4704</v>
       </c>
       <c r="V14" t="n">
         <v>-8.024000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2443</v>
+        <v>7.1598</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4061</v>
+        <v>3.7065</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8382</v>
+        <v>3.4533</v>
       </c>
       <c r="G15" t="n">
         <v>5.0293</v>
@@ -1624,13 +1624,13 @@
         <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5731000000000001</v>
+        <v>1.4885</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3094</v>
+        <v>0.6098</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2637</v>
+        <v>0.8787</v>
       </c>
       <c r="V15" t="n">
         <v>0.4489</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3304</v>
+        <v>3.8036</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7959</v>
+        <v>2.8946</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5346</v>
+        <v>0.909</v>
       </c>
       <c r="G16" t="n">
         <v>2.0005</v>
@@ -1702,13 +1702,13 @@
         <v>2.1231</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9559</v>
+        <v>1.4291</v>
       </c>
       <c r="T16" t="n">
-        <v>1.556</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3999</v>
+        <v>0.7743</v>
       </c>
       <c r="V16" t="n">
         <v>-1.5561</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6445</v>
+        <v>3.2099</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8905</v>
+        <v>1.59</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7541</v>
+        <v>1.6199</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1016</v>
@@ -1780,13 +1780,13 @@
         <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2479</v>
+        <v>0.8133</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3702</v>
+        <v>0.0697</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8778</v>
+        <v>0.7436</v>
       </c>
       <c r="V17" t="n">
         <v>2.4982</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3944</v>
+        <v>3.1159</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3574</v>
+        <v>1.7579</v>
       </c>
       <c r="F18" t="n">
-        <v>1.037</v>
+        <v>1.3579</v>
       </c>
       <c r="G18" t="n">
         <v>2.1295</v>
@@ -1858,13 +1858,13 @@
         <v>1.7371</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0985</v>
+        <v>0.623</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1943</v>
+        <v>0.2062</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0958</v>
+        <v>0.4167</v>
       </c>
       <c r="V18" t="n">
         <v>-0.4087</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2383</v>
+        <v>2.8484</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7942</v>
+        <v>1.5562</v>
       </c>
       <c r="F19" t="n">
-        <v>4.0325</v>
+        <v>1.2922</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1136</v>
+        <v>1.5119</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3385</v>
+        <v>-0.0382</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2249</v>
+        <v>1.5501</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6816</v>
+        <v>1.3645</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0516</v>
+        <v>0.0621</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7333</v>
+        <v>1.3024</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7952</v>
+        <v>0.1474</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2868</v>
+        <v>-0.1003</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5084</v>
+        <v>0.2478</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0881</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7371</v>
+        <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0199</v>
+        <v>0.5645</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1759</v>
+        <v>0.1917</v>
       </c>
       <c r="U19" t="n">
-        <v>0.844</v>
+        <v>0.3728</v>
       </c>
       <c r="V19" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1756</v>
+        <v>2.4515</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8892</v>
+        <v>-1.7942</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2864</v>
+        <v>4.2457</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2396</v>
+        <v>0.1136</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4906</v>
+        <v>0.3385</v>
       </c>
       <c r="I20" t="n">
-        <v>0.749</v>
+        <v>-0.2249</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3126</v>
+        <v>-0.6816</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6778</v>
+        <v>0.0516</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6348</v>
+        <v>-0.7333</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.073</v>
+        <v>0.7952</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1872</v>
+        <v>0.2868</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1142</v>
+        <v>0.5084</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.386</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.158</v>
+        <v>-3.0881</v>
       </c>
       <c r="R20" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2168</v>
+        <v>1.2331</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2208</v>
+        <v>0.1759</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.004</v>
+        <v>1.0572</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1052</v>
+        <v>2.4559</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5138</v>
+        <v>1.7997</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4087</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0737</v>
+        <v>2.323</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1556</v>
+        <v>1.6889</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9181</v>
+        <v>0.6341</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5119</v>
+        <v>1.2396</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0382</v>
+        <v>0.4906</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5501</v>
+        <v>0.749</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3645</v>
+        <v>1.3126</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0621</v>
+        <v>0.6778</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3024</v>
+        <v>0.6348</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1474</v>
+        <v>-0.073</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1003</v>
+        <v>-0.1872</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2478</v>
+        <v>0.1142</v>
       </c>
       <c r="P21" t="n">
-        <v>0.772</v>
+        <v>-0.386</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R21" t="n">
         <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2102</v>
+        <v>0.3642</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2089</v>
+        <v>0.0205</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0013</v>
+        <v>0.3437</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.1052</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8853</v>
+        <v>2.182</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4546</v>
+        <v>0.4583</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4307</v>
+        <v>1.7237</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6533</v>
+        <v>-0.4834</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9139</v>
+        <v>0.9967</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2606</v>
+        <v>-1.4801</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3145</v>
+        <v>0.1837</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3145</v>
+        <v>1.511</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.3273</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6612</v>
+        <v>-0.6671</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4006</v>
+        <v>-0.5143</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2606</v>
+        <v>-0.1528</v>
       </c>
       <c r="P22" t="n">
         <v>0.386</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>1.9896</v>
+        <v>1.1319</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4833</v>
+        <v>0.6256</v>
       </c>
       <c r="U22" t="n">
         <v>0.5063</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1631</v>
+        <v>1.1474</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2859</v>
+        <v>0.614</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1228</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.7757</v>
+        <v>2.0255</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2947</v>
+        <v>0.5863</v>
       </c>
       <c r="F23" t="n">
-        <v>4.0704</v>
+        <v>1.4392</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6984</v>
+        <v>-0.2342</v>
       </c>
       <c r="H23" t="n">
-        <v>0.119</v>
+        <v>1.653</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5794</v>
+        <v>-1.8871</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2373</v>
+        <v>0.0388</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2279</v>
+        <v>1.3661</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4652</v>
+        <v>-1.3273</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4611</v>
+        <v>-0.273</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3469</v>
+        <v>0.2868</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1142</v>
+        <v>-0.5598</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.3161</v>
+        <v>-0.386</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.0532</v>
+        <v>-0.965</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7371</v>
+        <v>0.579</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3934</v>
+        <v>0.4756</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2353</v>
+        <v>-0.0013</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1581</v>
+        <v>0.4769</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2.1701</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2859</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1434</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1857</v>
+        <v>-2.2947</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9576</v>
+        <v>3.267</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2342</v>
+        <v>1.6984</v>
       </c>
       <c r="H24" t="n">
-        <v>1.653</v>
+        <v>0.119</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8871</v>
+        <v>1.5794</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0388</v>
+        <v>1.2373</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3661</v>
+        <v>-0.2279</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3273</v>
+        <v>1.4652</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.273</v>
+        <v>0.4611</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2868</v>
+        <v>0.3469</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5598</v>
+        <v>0.1142</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.386</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.965</v>
+        <v>-4.0532</v>
       </c>
       <c r="R24" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4065</v>
+        <v>1.59</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4019</v>
+        <v>0.2353</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0046</v>
+        <v>1.3546</v>
       </c>
       <c r="V24" t="n">
-        <v>2.1701</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6562</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.1333</v>
+        <v>0.95</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2427</v>
+        <v>-0.3465</v>
       </c>
       <c r="F25" t="n">
-        <v>1.376</v>
+        <v>1.2965</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4834</v>
+        <v>-0.6533</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9967</v>
+        <v>-0.9139</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4801</v>
+        <v>0.2606</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1837</v>
+        <v>-1.3145</v>
       </c>
       <c r="K25" t="n">
-        <v>1.511</v>
+        <v>-1.3145</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3273</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6671</v>
+        <v>0.6612</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5143</v>
+        <v>0.4006</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1528</v>
+        <v>0.2606</v>
       </c>
       <c r="P25" t="n">
         <v>0.386</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0833</v>
+        <v>1.0543</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.6821</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1586</v>
+        <v>0.3721</v>
       </c>
       <c r="V25" t="n">
-        <v>1.1474</v>
+        <v>0.1631</v>
       </c>
       <c r="W25" t="n">
-        <v>0.614</v>
+        <v>0.2859</v>
       </c>
       <c r="X25" t="n">
-        <v>0.5334</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>29.0389</v>
+        <v>31.0419</v>
       </c>
       <c r="E26" t="n">
-        <v>9.8034</v>
+        <v>9.8033</v>
       </c>
       <c r="F26" t="n">
-        <v>19.2356</v>
+        <v>21.2385</v>
       </c>
       <c r="G26" t="n">
         <v>12.2503</v>
@@ -2452,13 +2452,13 @@
         <v>8.2126</v>
       </c>
       <c r="I26" t="n">
-        <v>4.037799999999999</v>
+        <v>4.0378</v>
       </c>
       <c r="J26" t="n">
         <v>10.9102</v>
       </c>
       <c r="K26" t="n">
-        <v>8.0145</v>
+        <v>8.014499999999998</v>
       </c>
       <c r="L26" t="n">
         <v>2.8956</v>
@@ -2467,13 +2467,13 @@
         <v>1.3401</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1979</v>
+        <v>0.1978999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>1.1424</v>
       </c>
       <c r="P26" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-9.999999999987796e-05</v>
       </c>
       <c r="Q26" t="n">
         <v>-14.4754</v>
@@ -2482,16 +2482,16 @@
         <v>14.4756</v>
       </c>
       <c r="S26" t="n">
-        <v>8.764699999999999</v>
+        <v>10.7675</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4705</v>
+        <v>3.4702</v>
       </c>
       <c r="U26" t="n">
-        <v>5.2943</v>
+        <v>7.296899999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>8.023999999999999</v>
+        <v>8.024000000000001</v>
       </c>
       <c r="W26" t="n">
         <v>9.898400000000001</v>
